--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486470_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486470_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0058</v>
+        <v>2.8152</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3607</v>
+        <v>0.386</v>
       </c>
       <c r="F2" t="n">
-        <v>2.645</v>
+        <v>2.4293</v>
       </c>
       <c r="G2" t="n">
         <v>2.1432</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3427</v>
+        <v>1.1521</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0106</v>
+        <v>1.0359</v>
       </c>
       <c r="U2" t="n">
-        <v>0.332</v>
+        <v>0.1163</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5544</v>
+        <v>1.2127</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3607</v>
+        <v>0.9318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9151</v>
+        <v>0.2809</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4962</v>
+        <v>-0.2583</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1336</v>
+        <v>0.666</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3626</v>
+        <v>-0.9243</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0365</v>
+        <v>-0.4311</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0365</v>
+        <v>0.0063</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.4374</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4597</v>
+        <v>0.1728</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.6597</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3626</v>
+        <v>-0.4869</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.137</v>
+        <v>1.601</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4951</v>
+        <v>1.8855</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6321</v>
+        <v>-0.2845</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1324</v>
+        <v>0.4679</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.056</v>
+        <v>-0.4472</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1884</v>
+        <v>0.9151</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2583</v>
+        <v>0.4962</v>
       </c>
       <c r="H4" t="n">
-        <v>0.666</v>
+        <v>0.1336</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9243</v>
+        <v>0.3626</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4311</v>
+        <v>0.0365</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0063</v>
+        <v>0.0365</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4374</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1728</v>
+        <v>0.4597</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6597</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4869</v>
+        <v>0.3626</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5207000000000001</v>
+        <v>-0.2235</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.4086</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.377</v>
+        <v>-0.6321</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1222</v>
+        <v>-0.1435</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6121</v>
+        <v>-0.1238</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4899</v>
+        <v>-0.0197</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6158</v>
+        <v>-1.2599</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.2899</v>
+        <v>0.9426</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3259</v>
+        <v>-2.2025</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.681</v>
+        <v>0.4758</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.7575</v>
+        <v>1.2775</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0765</v>
+        <v>-0.8016</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9348</v>
+        <v>-1.7357</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5324</v>
+        <v>-0.3348</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4024</v>
+        <v>-1.4009</v>
       </c>
       <c r="P5" t="n">
         <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3016</v>
+        <v>-0.0757</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8736</v>
+        <v>0.4879</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4279</v>
+        <v>-0.5636</v>
       </c>
       <c r="V5" t="n">
         <v>-0.113</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3082</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2405</v>
+        <v>-0.2407</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0213</v>
+        <v>-0.1331</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2618</v>
+        <v>-0.1075</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6917</v>
+        <v>-3.0016</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.255</v>
+        <v>-3.09</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4367</v>
+        <v>0.0885</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4534</v>
+        <v>-1.1678</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5681</v>
+        <v>-2.1257</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1147</v>
+        <v>0.9578</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2383</v>
+        <v>-1.8337</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3131</v>
+        <v>-0.9643</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5514</v>
+        <v>-0.8694</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2175</v>
+        <v>2.3926</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5589</v>
+        <v>0.3683</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4322</v>
+        <v>1.0347</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1267</v>
+        <v>-0.6663</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.0202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2525</v>
+        <v>-0.7625</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0399</v>
+        <v>1.376</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2924</v>
+        <v>-2.1385</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.0016</v>
+        <v>-0.6917</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.09</v>
+        <v>-0.255</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0885</v>
+        <v>-0.4367</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1678</v>
+        <v>-0.4534</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1257</v>
+        <v>-0.5681</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9578</v>
+        <v>0.1147</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8337</v>
+        <v>-0.2383</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9643</v>
+        <v>0.3131</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8694</v>
+        <v>-0.5514</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3564</v>
+        <v>2.0369</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2077</v>
+        <v>1.7869</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8512999999999999</v>
+        <v>0.2499</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-3.0202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7254</v>
+        <v>-1.2667</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4591</v>
+        <v>-1.1709</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2663</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2599</v>
+        <v>-2.6158</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9426</v>
+        <v>-2.2899</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2025</v>
+        <v>-0.3259</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4758</v>
+        <v>-1.681</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2775</v>
+        <v>-1.7575</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8016</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7357</v>
+        <v>-0.9348</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3348</v>
+        <v>-0.5324</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4009</v>
+        <v>-0.4024</v>
       </c>
       <c r="P8" t="n">
         <v>1.305</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6576</v>
+        <v>0.1571</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1526</v>
+        <v>0.3149</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8102</v>
+        <v>-0.1577</v>
       </c>
       <c r="V8" t="n">
         <v>-0.113</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.113</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6696</v>
+        <v>-1.4654</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2388</v>
+        <v>-1.1271</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4308</v>
+        <v>-0.3383</v>
       </c>
       <c r="G9" t="n">
         <v>0.5633</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7279</v>
+        <v>-0.5236</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3854</v>
+        <v>-0.2929</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8525</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9791</v>
+        <v>-2.6244</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9277</v>
+        <v>-3.573</v>
       </c>
       <c r="F10" t="n">
         <v>0.9486</v>
@@ -1234,10 +1234,10 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4527</v>
+        <v>1.8074</v>
       </c>
       <c r="T10" t="n">
-        <v>2.6618</v>
+        <v>2.0165</v>
       </c>
       <c r="U10" t="n">
         <v>-0.2091</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3811</v>
+        <v>-2.6498</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8974</v>
+        <v>-1.3819</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4836</v>
+        <v>-1.2679</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7442</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9387</v>
+        <v>-1.2074</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8904</v>
+        <v>-0.3749</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0482</v>
+        <v>-0.8325</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4382</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.299</v>
+        <v>-3.8644</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7578</v>
+        <v>-3.3541</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5412</v>
+        <v>-0.5104</v>
       </c>
       <c r="G12" t="n">
         <v>0.0452</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.4431</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5312</v>
+        <v>0.9349</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5226</v>
+        <v>-0.4918</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1777</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0827</v>
+        <v>-4.1681</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6781</v>
+        <v>-3.5785</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4046</v>
+        <v>-0.5896</v>
       </c>
       <c r="G13" t="n">
         <v>-5.1154</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4898</v>
+        <v>0.4248</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4554</v>
+        <v>0.6441</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0344</v>
+        <v>-0.2193</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5649999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.0595</v>
+        <v>-12.6897</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.5658</v>
+        <v>-12.1958</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4936999999999994</v>
+        <v>-0.4937000000000004</v>
       </c>
       <c r="G14" t="n">
         <v>-15.0007</v>
@@ -1534,7 +1534,7 @@
         <v>-0.6109</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.9564</v>
+        <v>-2.956399999999999</v>
       </c>
       <c r="P14" t="n">
         <v>2.175</v>
@@ -1546,19 +1546,19 @@
         <v>16.3129</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5905</v>
+        <v>5.960500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>8.574200000000001</v>
+        <v>9.944300000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.9837</v>
+        <v>-3.9836</v>
       </c>
       <c r="V14" t="n">
         <v>-5.824399999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>3.4313</v>
+        <v>3.431299999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-9.255699999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.0708</v>
+        <v>8.363799999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5674</v>
+        <v>6.0144</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5035</v>
+        <v>2.3493</v>
       </c>
       <c r="G15" t="n">
         <v>5.6034</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3803</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0721</v>
+        <v>0.5191</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4525</v>
+        <v>-0.6066</v>
       </c>
       <c r="V15" t="n">
         <v>1.3252</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7305</v>
+        <v>4.2912</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8607</v>
+        <v>3.6372</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8698</v>
+        <v>0.654</v>
       </c>
       <c r="G16" t="n">
         <v>1.6434</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1746</v>
+        <v>-0.2647</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4146</v>
+        <v>0.1911</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.24</v>
+        <v>-0.4558</v>
       </c>
       <c r="V16" t="n">
         <v>2.2599</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.761</v>
+        <v>3.1708</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9663</v>
+        <v>1.0781</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7947</v>
+        <v>2.0927</v>
       </c>
       <c r="G17" t="n">
         <v>2.4186</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0671</v>
+        <v>-0.6573</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1971</v>
+        <v>0.3088</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2642</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>-0.113</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7607</v>
+        <v>2.5067</v>
       </c>
       <c r="E18" t="n">
-        <v>1.76</v>
+        <v>1.383</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0007</v>
+        <v>1.1237</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0038</v>
+        <v>2.1291</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4354</v>
+        <v>1.0278</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4391</v>
+        <v>1.1013</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8001</v>
+        <v>1.204</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6631</v>
+        <v>0.0182</v>
       </c>
       <c r="L18" t="n">
-        <v>0.863</v>
+        <v>1.1857</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8038</v>
+        <v>0.9251</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2277</v>
+        <v>1.0096</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8444</v>
+        <v>-0.2749</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5622</v>
+        <v>0.1791</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7178</v>
+        <v>-0.4539</v>
       </c>
       <c r="V18" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6378</v>
+        <v>1.7471</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6066</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0312</v>
+        <v>1.2164</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1291</v>
+        <v>0.0038</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0278</v>
+        <v>-1.4354</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1013</v>
+        <v>1.4391</v>
       </c>
       <c r="J19" t="n">
-        <v>1.204</v>
+        <v>-0.8001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0182</v>
+        <v>-1.6631</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1857</v>
+        <v>0.863</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9251</v>
+        <v>0.8038</v>
       </c>
       <c r="N19" t="n">
-        <v>1.0096</v>
+        <v>0.2277</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1438</v>
+        <v>-0.1691</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4026</v>
+        <v>0.3329</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5464</v>
+        <v>-0.502</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.0854</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2467</v>
+        <v>1.595</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5705</v>
+        <v>1.3521</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6762</v>
+        <v>0.2429</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2511</v>
+        <v>4.0302</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4957</v>
+        <v>0.2674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7554</v>
+        <v>3.7628</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3137</v>
+        <v>3.1108</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4285</v>
+        <v>0.2222</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1147</v>
+        <v>2.8886</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5649</v>
+        <v>0.9194</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9242</v>
+        <v>0.0452</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6407</v>
+        <v>0.8741</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8035</v>
+        <v>-0.6474</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9718</v>
+        <v>0.2211</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1683</v>
+        <v>-0.8685</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.243</v>
+        <v>-0.4828</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.243</v>
+        <v>-0.678</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.725</v>
+        <v>0.8073</v>
       </c>
       <c r="E21" t="n">
         <v>-0.9089</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6338</v>
+        <v>1.7161</v>
       </c>
       <c r="G21" t="n">
         <v>0.9719</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2311</v>
+        <v>0.3133</v>
       </c>
       <c r="T21" t="n">
         <v>0.4026</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1715</v>
+        <v>-0.0892</v>
       </c>
       <c r="V21" t="n">
         <v>0.1745</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4851</v>
+        <v>0.6949</v>
       </c>
       <c r="E22" t="n">
-        <v>0.458</v>
+        <v>-0.2176</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0271</v>
+        <v>0.9125</v>
       </c>
       <c r="G22" t="n">
-        <v>4.0302</v>
+        <v>1.2511</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2674</v>
+        <v>0.4957</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7628</v>
+        <v>0.7554</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1108</v>
+        <v>-0.3137</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2222</v>
+        <v>-0.4285</v>
       </c>
       <c r="L22" t="n">
-        <v>2.8886</v>
+        <v>0.1147</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9194</v>
+        <v>1.5649</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0452</v>
+        <v>0.9242</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8741</v>
+        <v>0.6407</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7572</v>
+        <v>0.2518</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6729000000000001</v>
+        <v>1.1837</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0843</v>
+        <v>-0.9319</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.4828</v>
+        <v>-1.243</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.678</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9796</v>
+        <v>-0.0149</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5208</v>
+        <v>-2.515</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5412</v>
+        <v>2.5001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8729</v>
@@ -2248,13 +2248,13 @@
         <v>2.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7762</v>
+        <v>-0.8114</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8904</v>
+        <v>0.1154</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8858</v>
+        <v>-0.9268</v>
       </c>
       <c r="V23" t="n">
         <v>1.582</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8588</v>
+        <v>-3.6224</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2571</v>
+        <v>-5.3796</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3983</v>
+        <v>1.7573</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0809</v>
+        <v>-0.0969</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8395</v>
+        <v>0.5716</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2415</v>
+        <v>-0.6686</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3406</v>
+        <v>-1.4793</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4171</v>
+        <v>-0.4681</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0765</v>
+        <v>-1.0112</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2597</v>
+        <v>1.3824</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5776</v>
+        <v>1.0398</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.318</v>
+        <v>0.3426</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3926</v>
+        <v>-3.9151</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.2626</v>
+        <v>-5.4377</v>
       </c>
       <c r="R24" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0052</v>
+        <v>-0.6273</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3461</v>
+        <v>0.4074</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3409</v>
+        <v>-1.0347</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3904</v>
+        <v>1.017</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3904</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5196</v>
+        <v>-3.9898</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.609</v>
+        <v>-4.4806</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0894</v>
+        <v>0.4908</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0969</v>
+        <v>-1.0809</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5716</v>
+        <v>-0.8395</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6686</v>
+        <v>-0.2415</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.4793</v>
+        <v>-1.3406</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4681</v>
+        <v>-1.4171</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.0112</v>
+        <v>0.0765</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3824</v>
+        <v>0.2597</v>
       </c>
       <c r="N25" t="n">
-        <v>1.0398</v>
+        <v>0.5776</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3426</v>
+        <v>-0.318</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.9151</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.4377</v>
+        <v>-3.2626</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.5245</v>
+        <v>-0.1259</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.822</v>
+        <v>0.1226</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7026</v>
+        <v>-0.2485</v>
       </c>
       <c r="V25" t="n">
-        <v>1.017</v>
+        <v>-0.3904</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.113</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="26">
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>14.0596</v>
+        <v>15.5497</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4937000000000014</v>
+        <v>0.4937999999999994</v>
       </c>
       <c r="F26" t="n">
-        <v>13.5659</v>
+        <v>15.0558</v>
       </c>
       <c r="G26" t="n">
-        <v>15.0008</v>
+        <v>15.00079999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>8.195399999999999</v>
+        <v>8.195400000000001</v>
       </c>
       <c r="I26" t="n">
         <v>6.8051</v>
@@ -2458,7 +2458,7 @@
         <v>3.567399999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6109999999999995</v>
+        <v>0.6110000000000002</v>
       </c>
       <c r="L26" t="n">
         <v>2.956299999999999</v>
@@ -2482,16 +2482,16 @@
         <v>14.1376</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.5903</v>
+        <v>-3.1003</v>
       </c>
       <c r="T26" t="n">
         <v>3.9838</v>
       </c>
       <c r="U26" t="n">
-        <v>-8.574299999999999</v>
+        <v>-7.0841</v>
       </c>
       <c r="V26" t="n">
-        <v>5.824399999999999</v>
+        <v>5.824400000000001</v>
       </c>
       <c r="W26" t="n">
         <v>9.255700000000001</v>
